--- a/etf_holdings/2026-09-15_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:38</t>
+          <t>2026-09-15 19:51:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.24%2380</t>
+          <t>+0.21%2385</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2380</v>
+        <v>2385</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.45%753,000</t>
+          <t>9.42%753,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.45%</t>
+          <t>9.42%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:38</t>
+          <t>2026-09-15 19:51:38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.55%4560</t>
+          <t>-2.85%4430</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4560</v>
+        <v>4430</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.95%249,000</t>
+          <t>5.97%249,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.95%</t>
+          <t>5.97%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:38</t>
+          <t>2026-09-15 19:51:38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.75%11990</t>
+          <t>-2.29%11715</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-2.29%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>11990</v>
+        <v>11715</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.21%67,000</t>
+          <t>4.22%67,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.21%</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:38</t>
+          <t>2026-09-15 19:51:38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.37%5345</t>
+          <t>-4.3%5115</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5345</v>
+        <v>5115</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.80%136,000</t>
+          <t>3.82%136,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>3.82%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:38</t>
+          <t>2026-09-15 19:51:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0%1620</t>
+          <t>+3.09%1670</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1620</v>
+        <v>1670</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.41%404,000</t>
+          <t>3.44%404,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.44%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:38</t>
+          <t>2026-09-15 19:51:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.72%970</t>
+          <t>-1.96%951</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>970</v>
+        <v>951</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:38</t>
+          <t>2026-09-15 19:51:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.21%234</t>
+          <t>-5.34%221.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-5.34%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>234</v>
+        <v>221.5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.95%2,416,000</t>
+          <t>2.97%2,416,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.97%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:38</t>
+          <t>2026-09-15 19:51:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-4.06%473</t>
+          <t>-1.59%465.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-4.06%</t>
+          <t>-1.59%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>473</v>
+        <v>465.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.81%1,096,000</t>
+          <t>2.73%1,096,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.73%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:38</t>
+          <t>2026-09-15 19:51:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.2%248.5</t>
+          <t>-0.8%246.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>248.5</v>
+        <v>246.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.48%1,921,000</t>
+          <t>2.51%1,921,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.51%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:38</t>
+          <t>2026-09-15 19:51:38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.08%6305</t>
+          <t>-2.7%6135</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>6305</v>
+        <v>6135</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.40%73,000</t>
+          <t>2.42%73,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:38</t>
+          <t>2026-09-15 19:51:38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.78%3310</t>
+          <t>-5.89%3115</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-5.89%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3310</v>
+        <v>3115</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.35%134,000</t>
+          <t>2.33%134,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:38</t>
+          <t>2026-09-15 19:51:38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.71%2810</t>
+          <t>-2.55%2675</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>-2.55%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2810</v>
+        <v>2675</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.20%150,600</t>
+          <t>2.17%150,600</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:38</t>
+          <t>2026-09-15 19:51:38</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2368金像電子（股）公司</t>
+          <t>6223旺矽科技</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.97%1020</t>
+          <t>-2.77%5440</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1020</v>
+        <v>5440</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.11%393,000</t>
+          <t>2.12%72,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.12%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>393000</v>
+        <v>72000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:38</t>
+          <t>2026-09-15 19:51:38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,25 +1297,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6223旺矽科技</t>
+          <t>3653健策精密工業</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0%5620</t>
+          <t>-8.76%5310</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-8.76%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5620</v>
+        <v>5310</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.11%72,000</t>
+          <t>2.11%69,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1324,11 +1324,11 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>72000</v>
+        <v>69000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:38</t>
+          <t>2026-09-15 19:51:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3653健策精密工業</t>
+          <t>2368金像電子（股）公司</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.95%5820</t>
+          <t>-4.71%972</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>-4.71%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5820</v>
+        <v>972</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.07%69,000</t>
+          <t>2.11%393,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>69000</v>
+        <v>393000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:39</t>
+          <t>2026-09-15 19:51:39</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2344華邦電子</t>
+          <t>3711日月光投資控股</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-6.71%160</t>
+          <t>-3.27%592</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.71%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>160</v>
+        <v>592</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.05%2,293,000</t>
+          <t>2.00%621,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2293000</v>
+        <v>621000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:39</t>
+          <t>2026-09-15 19:51:39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3711日月光投資控股</t>
+          <t>3443創意電子</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.97%612</t>
+          <t>-5.7%6035</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>612</v>
+        <v>6035</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.00%621,000</t>
+          <t>1.99%59,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>621000</v>
+        <v>59000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:39</t>
+          <t>2026-09-15 19:51:39</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6515穎崴科技</t>
+          <t>2344華邦電子</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-4.21%6600</t>
+          <t>-0.31%159.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-4.21%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6600</v>
+        <v>159.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.97%55,000</t>
+          <t>1.93%2,293,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>55000</v>
+        <v>2293000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:39</t>
+          <t>2026-09-15 19:51:39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-4.36%17885</t>
+          <t>-2.56%17520</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>-2.56%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>17885</v>
+        <v>17520</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.89%20,300</t>
+          <t>1.92%20,300</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.92%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:39</t>
+          <t>2026-09-15 19:51:39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3443創意電子</t>
+          <t>6515穎崴科技</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+4.58%6400</t>
+          <t>-4.39%6310</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+4.58%</t>
+          <t>-4.39%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6400</v>
+        <v>6310</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.88%59,000</t>
+          <t>1.91%55,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>59000</v>
+        <v>55000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:39</t>
+          <t>2026-09-15 19:51:39</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.73%2270</t>
+          <t>+1.98%2315</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2270</v>
+        <v>2315</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.87%155,105</t>
+          <t>1.85%155,105</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:39</t>
+          <t>2026-09-15 19:51:39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>8299群聯電子</t>
+          <t>6274台燿科技</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-3.63%1990</t>
+          <t>-2.84%1370</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-3.63%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1990</v>
+        <v>1370</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.74%168,000</t>
+          <t>1.78%240,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.78%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>168000</v>
+        <v>240000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:39</t>
+          <t>2026-09-15 19:51:39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-1.19%332.5</t>
+          <t>+0.15%333</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>332.5</v>
+        <v>333</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:39</t>
+          <t>2026-09-15 19:51:39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-0.53%1875</t>
+          <t>-1.87%1840</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1875</v>
+        <v>1840</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.71%174,000</t>
+          <t>1.72%174,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:39</t>
+          <t>2026-09-15 19:51:39</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,25 +1968,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6274台燿科技</t>
+          <t>8299群聯電子</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-2.15%1365</t>
+          <t>-0.78%1920</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1365</v>
+        <v>1920</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.71%240,000</t>
+          <t>1.71%168,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1995,11 +1995,11 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>240000</v>
+        <v>168000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:39</t>
+          <t>2026-09-15 19:51:39</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,25 +2034,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+0.18%545</t>
+          <t>-1.47%537</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.69%595,000</t>
+          <t>1.70%595,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:39</t>
+          <t>2026-09-15 19:51:39</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-0.93%2140</t>
+          <t>-2.8%2080</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2140</v>
+        <v>2080</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.66%148,000</t>
+          <t>1.67%148,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:39</t>
+          <t>2026-09-15 19:51:39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+0.11%46.35</t>
+          <t>-1.51%45.65</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>46.35</v>
+        <v>45.65</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.53%6,340,622</t>
+          <t>1.55%6,340,622</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:39</t>
+          <t>2026-09-15 19:51:39</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-2.31%1055</t>
+          <t>+2.84%1085</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1055</v>
+        <v>1085</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.41%251,000</t>
+          <t>1.39%251,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:39</t>
+          <t>2026-09-15 19:51:39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+1.49%68.1</t>
+          <t>+2.35%69.7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+1.49%</t>
+          <t>+2.35%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>68.09999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.29%3,699,000</t>
+          <t>1.32%3,699,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:40</t>
+          <t>2026-09-15 19:51:41</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,25 +2339,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+1.18%515</t>
+          <t>+0.78%519</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+1.18%</t>
+          <t>+0.78%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.28%482,000</t>
+          <t>1.31%482,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:40</t>
+          <t>2026-09-15 19:51:41</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-1.43%344</t>
+          <t>-0.29%343</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:40</t>
+          <t>2026-09-15 19:51:41</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-2.43%181</t>
+          <t>+0.83%182.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2.43%</t>
+          <t>+0.83%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>181</v>
+        <v>182.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.25%1,298,000</t>
+          <t>1.24%1,298,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:40</t>
+          <t>2026-09-15 19:51:41</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>8996高力熱處理工業</t>
+          <t>3189景碩科技</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-7.14%1235</t>
+          <t>-0.38%795</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-7.14%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1235</v>
+        <v>795</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.25%181,000</t>
+          <t>1.21%289,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>181000</v>
+        <v>289000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:40</t>
+          <t>2026-09-15 19:51:41</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3189景碩科技</t>
+          <t>5904寶雅國際</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-2.92%798</t>
+          <t>+0.14%73</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-2.92%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>798</v>
+        <v>73</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.24%289,000</t>
+          <t>1.20%3,124,500</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>289000</v>
+        <v>3124500</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:40</t>
+          <t>2026-09-15 19:51:41</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>5904寶雅國際</t>
+          <t>8996高力熱處理工業</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+1.12%72.3</t>
+          <t>-1.21%1220</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+1.12%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>72.3</v>
+        <v>1220</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.18%3,124,500</t>
+          <t>1.18%181,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,11 +2666,11 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>3124500</v>
+        <v>181000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:40</t>
+          <t>2026-09-15 19:51:41</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.52%192</t>
+          <t>+0.26%192.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>192</v>
+        <v>192.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.14%1,147,000</t>
+          <t>1.16%1,147,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:40</t>
+          <t>2026-09-15 19:51:41</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.56%693</t>
+          <t>-0.43%696</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.91%252,000</t>
+          <t>0.93%252,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:40</t>
+          <t>2026-09-15 19:51:41</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+0.39%510</t>
+          <t>-3.82%490.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-3.82%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>510</v>
+        <v>490.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.91%345,000</t>
+          <t>0.93%345,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:40</t>
+          <t>2026-09-15 19:51:41</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-1.75%731</t>
+          <t>-0.68%726</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:40</t>
+          <t>2026-09-15 19:51:41</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-9.98%5995</t>
+          <t>+1%6055</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-9.98%</t>
+          <t>+1%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>5995</v>
+        <v>6055</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.90%26,000</t>
+          <t>0.82%26,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:40</t>
+          <t>2026-09-15 19:51:41</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-3.96%230.5</t>
+          <t>-2.86%221</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-3.96%</t>
+          <t>-2.86%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>230.5</v>
+        <v>221</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:40</t>
+          <t>2026-09-15 19:51:41</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.11%489.5</t>
+          <t>-2.45%477.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.11%</t>
+          <t>-2.45%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>489.5</v>
+        <v>477.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:40</t>
+          <t>2026-09-15 19:51:41</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>3529力旺電子</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.7%2165</t>
+          <t>-3.85%2625</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>-3.85%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2165</v>
+        <v>2625</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.60%54,000</t>
+          <t>0.63%44,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>54000</v>
+        <v>44000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:40</t>
+          <t>2026-09-15 19:51:41</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,38 +3188,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3529力旺電子</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-5.49%2580</t>
+          <t>-6.47%2025</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-5.49%</t>
+          <t>-6.47%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2580</v>
+        <v>2025</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.59%44,000</t>
+          <t>0.61%54,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>44000</v>
+        <v>54000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:42</t>
+          <t>2026-09-15 19:51:42</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,25 +3254,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-4.59%541</t>
+          <t>-5.18%513</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-4.59%</t>
+          <t>-5.18%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>541</v>
+        <v>513</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.54%182,000</t>
+          <t>0.52%182,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:42</t>
+          <t>2026-09-15 19:51:42</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,25 +3315,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+4.27%1955</t>
+          <t>+1.28%1980</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+4.27%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1955</v>
+        <v>1980</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.47%48,336</t>
+          <t>0.50%48,336</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:42</t>
+          <t>2026-09-15 19:51:42</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,25 +3376,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.56%886</t>
+          <t>-1.35%874</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>-1.35%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>886</v>
+        <v>874</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.45%95,000</t>
+          <t>0.44%95,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:42</t>
+          <t>2026-09-15 19:51:42</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,25 +3437,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-4.79%1590</t>
+          <t>-5.03%1510</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-4.79%</t>
+          <t>-5.03%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1590</v>
+        <v>1510</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.33%38,000</t>
+          <t>0.32%38,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:42</t>
+          <t>2026-09-15 19:51:42</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+0.63%1590</t>
+          <t>-4.4%1520</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1590</v>
+        <v>1520</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-09-15_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:38</t>
+          <t>2026-09-15 21:11:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:38</t>
+          <t>2026-09-15 21:11:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:38</t>
+          <t>2026-09-15 21:11:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:38</t>
+          <t>2026-09-15 21:11:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:38</t>
+          <t>2026-09-15 21:11:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:38</t>
+          <t>2026-09-15 21:11:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:38</t>
+          <t>2026-09-15 21:11:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:38</t>
+          <t>2026-09-15 21:11:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:38</t>
+          <t>2026-09-15 21:11:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:38</t>
+          <t>2026-09-15 21:11:58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:38</t>
+          <t>2026-09-15 21:11:58</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:38</t>
+          <t>2026-09-15 21:11:58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:38</t>
+          <t>2026-09-15 21:11:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:38</t>
+          <t>2026-09-15 21:11:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:38</t>
+          <t>2026-09-15 21:11:58</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:39</t>
+          <t>2026-09-15 21:11:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:39</t>
+          <t>2026-09-15 21:11:59</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:39</t>
+          <t>2026-09-15 21:11:59</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:39</t>
+          <t>2026-09-15 21:11:59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:39</t>
+          <t>2026-09-15 21:11:59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:39</t>
+          <t>2026-09-15 21:11:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:39</t>
+          <t>2026-09-15 21:11:59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:39</t>
+          <t>2026-09-15 21:11:59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:39</t>
+          <t>2026-09-15 21:11:59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:39</t>
+          <t>2026-09-15 21:11:59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:39</t>
+          <t>2026-09-15 21:11:59</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:39</t>
+          <t>2026-09-15 21:11:59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:39</t>
+          <t>2026-09-15 21:11:59</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:39</t>
+          <t>2026-09-15 21:11:59</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:39</t>
+          <t>2026-09-15 21:11:59</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:41</t>
+          <t>2026-09-15 21:12:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:41</t>
+          <t>2026-09-15 21:12:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:41</t>
+          <t>2026-09-15 21:12:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:41</t>
+          <t>2026-09-15 21:12:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:41</t>
+          <t>2026-09-15 21:12:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:41</t>
+          <t>2026-09-15 21:12:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:41</t>
+          <t>2026-09-15 21:12:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:41</t>
+          <t>2026-09-15 21:12:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:41</t>
+          <t>2026-09-15 21:12:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:41</t>
+          <t>2026-09-15 21:12:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:41</t>
+          <t>2026-09-15 21:12:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:41</t>
+          <t>2026-09-15 21:12:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:41</t>
+          <t>2026-09-15 21:12:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:41</t>
+          <t>2026-09-15 21:12:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:41</t>
+          <t>2026-09-15 21:12:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:42</t>
+          <t>2026-09-15 21:12:02</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:42</t>
+          <t>2026-09-15 21:12:02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:42</t>
+          <t>2026-09-15 21:12:02</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:42</t>
+          <t>2026-09-15 21:12:02</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:42</t>
+          <t>2026-09-15 21:12:02</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-15_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:58</t>
+          <t>2026-09-15 22:22:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:58</t>
+          <t>2026-09-15 22:22:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:58</t>
+          <t>2026-09-15 22:22:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:58</t>
+          <t>2026-09-15 22:22:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:58</t>
+          <t>2026-09-15 22:22:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:58</t>
+          <t>2026-09-15 22:22:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:58</t>
+          <t>2026-09-15 22:22:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:58</t>
+          <t>2026-09-15 22:22:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:58</t>
+          <t>2026-09-15 22:22:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:58</t>
+          <t>2026-09-15 22:22:16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:58</t>
+          <t>2026-09-15 22:22:16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:58</t>
+          <t>2026-09-15 22:22:16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:58</t>
+          <t>2026-09-15 22:22:16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:58</t>
+          <t>2026-09-15 22:22:16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:58</t>
+          <t>2026-09-15 22:22:16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:59</t>
+          <t>2026-09-15 22:22:17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:59</t>
+          <t>2026-09-15 22:22:17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:59</t>
+          <t>2026-09-15 22:22:17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:59</t>
+          <t>2026-09-15 22:22:17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:59</t>
+          <t>2026-09-15 22:22:17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:59</t>
+          <t>2026-09-15 22:22:17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:59</t>
+          <t>2026-09-15 22:22:17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:59</t>
+          <t>2026-09-15 22:22:17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:59</t>
+          <t>2026-09-15 22:22:17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:59</t>
+          <t>2026-09-15 22:22:17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:59</t>
+          <t>2026-09-15 22:22:17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:59</t>
+          <t>2026-09-15 22:22:17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:59</t>
+          <t>2026-09-15 22:22:17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:59</t>
+          <t>2026-09-15 22:22:17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:59</t>
+          <t>2026-09-15 22:22:17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:00</t>
+          <t>2026-09-15 22:22:18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:00</t>
+          <t>2026-09-15 22:22:18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:00</t>
+          <t>2026-09-15 22:22:18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:00</t>
+          <t>2026-09-15 22:22:18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:00</t>
+          <t>2026-09-15 22:22:18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:00</t>
+          <t>2026-09-15 22:22:18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:00</t>
+          <t>2026-09-15 22:22:18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:00</t>
+          <t>2026-09-15 22:22:18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:00</t>
+          <t>2026-09-15 22:22:18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:00</t>
+          <t>2026-09-15 22:22:18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:00</t>
+          <t>2026-09-15 22:22:18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:00</t>
+          <t>2026-09-15 22:22:18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:00</t>
+          <t>2026-09-15 22:22:18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:00</t>
+          <t>2026-09-15 22:22:18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:00</t>
+          <t>2026-09-15 22:22:18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:02</t>
+          <t>2026-09-15 22:22:20</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:02</t>
+          <t>2026-09-15 22:22:20</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:02</t>
+          <t>2026-09-15 22:22:20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:02</t>
+          <t>2026-09-15 22:22:20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:02</t>
+          <t>2026-09-15 22:22:20</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-15_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:16</t>
+          <t>2026-09-15 22:27:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:16</t>
+          <t>2026-09-15 22:27:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:16</t>
+          <t>2026-09-15 22:27:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:16</t>
+          <t>2026-09-15 22:27:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:16</t>
+          <t>2026-09-15 22:27:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:16</t>
+          <t>2026-09-15 22:27:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:16</t>
+          <t>2026-09-15 22:27:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:16</t>
+          <t>2026-09-15 22:27:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:16</t>
+          <t>2026-09-15 22:27:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:16</t>
+          <t>2026-09-15 22:27:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:16</t>
+          <t>2026-09-15 22:27:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:16</t>
+          <t>2026-09-15 22:27:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:16</t>
+          <t>2026-09-15 22:27:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:16</t>
+          <t>2026-09-15 22:27:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:16</t>
+          <t>2026-09-15 22:27:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:17</t>
+          <t>2026-09-15 22:27:40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:17</t>
+          <t>2026-09-15 22:27:40</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:17</t>
+          <t>2026-09-15 22:27:40</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:17</t>
+          <t>2026-09-15 22:27:40</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:17</t>
+          <t>2026-09-15 22:27:40</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:17</t>
+          <t>2026-09-15 22:27:40</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:17</t>
+          <t>2026-09-15 22:27:40</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:17</t>
+          <t>2026-09-15 22:27:40</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:17</t>
+          <t>2026-09-15 22:27:40</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:17</t>
+          <t>2026-09-15 22:27:40</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:17</t>
+          <t>2026-09-15 22:27:40</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:17</t>
+          <t>2026-09-15 22:27:40</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:17</t>
+          <t>2026-09-15 22:27:40</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:17</t>
+          <t>2026-09-15 22:27:40</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:17</t>
+          <t>2026-09-15 22:27:40</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:18</t>
+          <t>2026-09-15 22:27:41</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:18</t>
+          <t>2026-09-15 22:27:41</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:18</t>
+          <t>2026-09-15 22:27:41</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:18</t>
+          <t>2026-09-15 22:27:41</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:18</t>
+          <t>2026-09-15 22:27:41</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:18</t>
+          <t>2026-09-15 22:27:41</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:18</t>
+          <t>2026-09-15 22:27:41</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:18</t>
+          <t>2026-09-15 22:27:41</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:18</t>
+          <t>2026-09-15 22:27:41</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:18</t>
+          <t>2026-09-15 22:27:41</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:18</t>
+          <t>2026-09-15 22:27:41</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:18</t>
+          <t>2026-09-15 22:27:41</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:18</t>
+          <t>2026-09-15 22:27:41</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:18</t>
+          <t>2026-09-15 22:27:41</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:18</t>
+          <t>2026-09-15 22:27:41</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:20</t>
+          <t>2026-09-15 22:27:42</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:20</t>
+          <t>2026-09-15 22:27:42</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:20</t>
+          <t>2026-09-15 22:27:42</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:20</t>
+          <t>2026-09-15 22:27:42</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:20</t>
+          <t>2026-09-15 22:27:42</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
